--- a/jpcore-r4/develop-kohetest/StructureDefinition-jp-medication-ingredientstrength-strengthtype.xlsx
+++ b/jpcore-r4/develop-kohetest/StructureDefinition-jp-medication-ingredientstrength-strengthtype.xlsx
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Extension</t>
+    <t>http://hl7.org/fhir/StructureDefinition/Extension|4.0.1</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -353,7 +353,7 @@
     <t>example</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationIngredientStrengthStrengthType_VS</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationIngredientStrengthStrengthType_VS|1.1.0a</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
@@ -699,7 +699,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="18.49609375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="66.17578125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="71.66796875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>

--- a/jpcore-r4/develop-kohetest/StructureDefinition-jp-medication-ingredientstrength-strengthtype.xlsx
+++ b/jpcore-r4/develop-kohetest/StructureDefinition-jp-medication-ingredientstrength-strengthtype.xlsx
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Extension|4.0.1</t>
+    <t>http://hl7.org/fhir/StructureDefinition/Extension</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -353,7 +353,7 @@
     <t>example</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationIngredientStrengthStrengthType_VS|1.1.0a</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationIngredientStrengthStrengthType_VS</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
@@ -699,7 +699,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="18.49609375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="71.66796875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="66.17578125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
